--- a/data/por_departamento/Morazán/establecimientos_salud.xlsx
+++ b/data/por_departamento/Morazán/establecimientos_salud.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Establecimientos" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Establecimientos'!$A$1:$AA$49</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Establecimientos'!$A$1:$AA$47</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA49"/>
+  <dimension ref="A1:AA47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2232,7 +2232,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>geofabrik-way-8328359</t>
+          <t>geofabrik-way-1137560891</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2242,12 +2242,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>way/8328359</t>
+          <t>way/1137560891</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Hospital Nacional de San Francisco Gotera</t>
+          <t>Centro de Salud Chilanga</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -2262,12 +2262,12 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Predio</t>
+          <t>Edificio</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>predio</t>
+          <t>edificio</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2277,7 +2277,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>San Francisco Gotera</t>
+          <t>Chilanga</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -2292,17 +2292,17 @@
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>13.6978931</t>
+          <t>13.72142841</t>
         </is>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>-88.10190785</t>
+          <t>-88.12073759</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -2312,24 +2312,24 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>POLYGON ((-88.1022721 13.6984445, -88.1015783 13.6984618, -88.1015533 13.6975703, -88.1015382 13.6975709, -88.101528 13.6973426, -88.1022433 13.6973338, -88.1022721 13.6984445))</t>
+          <t>POLYGON ((-88.1208776 13.7214627, -88.1208141 13.7214629, -88.1208143 13.7215305, -88.1206547 13.7215309, -88.1206546 13.7214674, -88.1206015 13.7214676, -88.1206012 13.7213475, -88.1208773 13.7213467, -88.1208776 13.7214627))</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/way/8328359</t>
+          <t>https://www.openstreetmap.org/way/1137560891</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=13.6978931,-88.10190785</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=13.72142841,-88.12073759</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>geofabrik-way-1137560891</t>
+          <t>geofabrik-node-8038414002</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2339,32 +2339,32 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>way/1137560891</t>
+          <t>node/8038414002</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Centro de Salud Chilanga</t>
+          <t>Sin nombre</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Hospital</t>
+          <t>Consultorio</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>hospital</t>
+          <t>consultorio</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Edificio</t>
+          <t>Punto</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>edificio</t>
+          <t>punto</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2374,7 +2374,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Chilanga</t>
+          <t>El Divisadero</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -2384,64 +2384,64 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>Polygon</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>13.72142841</t>
+          <t>13.5769823</t>
         </is>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>-88.12073759</t>
+          <t>-88.1278297</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>centroide_area</t>
+          <t>coordenada_original</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>POLYGON ((-88.1208776 13.7214627, -88.1208141 13.7214629, -88.1208143 13.7215305, -88.1206547 13.7215309, -88.1206546 13.7214674, -88.1206015 13.7214676, -88.1206012 13.7213475, -88.1208773 13.7213467, -88.1208776 13.7214627))</t>
+          <t>POINT (-88.1278297 13.5769823)</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/way/1137560891</t>
+          <t>https://www.openstreetmap.org/node/8038414002</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=13.72142841,-88.12073759</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=13.5769823,-88.1278297</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>geofabrik-node-7223662570</t>
+          <t>hot-way-401307201</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>geofabrik</t>
+          <t>hot</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>node/7223662570</t>
+          <t>way/401307201</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Clinica El Mozote</t>
+          <t>Unidad de Salud</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -2456,12 +2456,12 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Punto</t>
+          <t>Polígono</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>punto</t>
+          <t>poligono</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Arambala</t>
+          <t>San Simón</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -2481,84 +2481,84 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>Point</t>
+          <t>Polygon</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>13.8988504</t>
+          <t>13.83890875</t>
         </is>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>-88.1144685</t>
+          <t>-88.26617586</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>coordenada_original</t>
+          <t>centroide_area</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>POINT (-88.1144685 13.8988504)</t>
+          <t>POLYGON ((-88.2662884 13.8388631, -88.2662532 13.8388919, -88.2662939 13.8389388, -88.2662256 13.8389946, -88.266185 13.8389479, -88.2661018 13.8390159, -88.266035 13.8389389, -88.2662217 13.8387862, -88.2662884 13.8388631))</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/node/7223662570</t>
+          <t>https://www.openstreetmap.org/way/401307201</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=13.8988504,-88.1144685</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=13.83890875,-88.26617586</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>geofabrik-node-8038414002</t>
+          <t>hot-relation-8328359</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>geofabrik</t>
+          <t>hot</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>node/8038414002</t>
+          <t>relation/8328359</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Sin nombre</t>
+          <t>Hospital Nacional de San Francisco Gotera</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Consultorio</t>
+          <t>Hospital</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>consultorio</t>
+          <t>hospital</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Punto</t>
+          <t>Polígono</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>punto</t>
+          <t>poligono</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2568,7 +2568,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>El Divisadero</t>
+          <t>San Francisco Gotera</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -2576,51 +2576,71 @@
           <t>Oriental</t>
         </is>
       </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>Público</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Medicina general</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>hospital</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>hospital</t>
+        </is>
+      </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>Point</t>
+          <t>Polygon</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>13.5769823</t>
+          <t>13.6978931</t>
         </is>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>-88.1278297</t>
+          <t>-88.10190785</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>coordenada_original</t>
+          <t>centroide_area</t>
         </is>
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>POINT (-88.1278297 13.5769823)</t>
+          <t>POLYGON ((-88.1015783 13.6984618, -88.1022721 13.6984445, -88.1022433 13.6973338, -88.101528 13.6973426, -88.1015382 13.6975709, -88.1015533 13.6975703, -88.1015783 13.6984618))</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/node/8038414002</t>
+          <t>https://www.openstreetmap.org/relation/8328359</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=13.5769823,-88.1278297</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=13.6978931,-88.10190785</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>hot-way-401307201</t>
+          <t>hot-way-850616743</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2630,22 +2650,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>way/401307201</t>
+          <t>way/850616743</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Unidad de Salud</t>
+          <t>sibasi</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Clínica</t>
+          <t>Otro</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>clinica</t>
+          <t>otro</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -2665,7 +2685,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>San Simón</t>
+          <t>San Francisco Gotera</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -2680,17 +2700,17 @@
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>13.83890875</t>
+          <t>13.69862207</t>
         </is>
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>-88.26617586</t>
+          <t>-88.10189578</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -2700,24 +2720,24 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>POLYGON ((-88.2662884 13.8388631, -88.2662532 13.8388919, -88.2662939 13.8389388, -88.2662256 13.8389946, -88.266185 13.8389479, -88.2661018 13.8390159, -88.266035 13.8389389, -88.2662217 13.8387862, -88.2662884 13.8388631))</t>
+          <t>POLYGON ((-88.1021602 13.6987283, -88.102248 13.6984719, -88.1016197 13.6984768, -88.1016163 13.6988229, -88.1021602 13.6987283))</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/way/401307201</t>
+          <t>https://www.openstreetmap.org/way/850616743</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=13.83890875,-88.26617586</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=13.69862207,-88.10189578</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>hot-relation-8328359</t>
+          <t>hot-node-3972391822</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2727,32 +2747,32 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>relation/8328359</t>
+          <t>node/3972391822</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Hospital Nacional de San Francisco Gotera</t>
+          <t>Unidad de Salud</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Hospital</t>
+          <t>Clínica</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>hospital</t>
+          <t>clinica</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Polígono</t>
+          <t>Punto</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>poligono</t>
+          <t>punto</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -2762,7 +2782,7 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>San Francisco Gotera</t>
+          <t>Delicias de Concepción</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -2770,71 +2790,51 @@
           <t>Oriental</t>
         </is>
       </c>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>Público</t>
-        </is>
-      </c>
-      <c r="P24" t="inlineStr">
-        <is>
-          <t>Medicina general</t>
-        </is>
-      </c>
-      <c r="Q24" t="inlineStr">
-        <is>
-          <t>hospital</t>
-        </is>
-      </c>
-      <c r="R24" t="inlineStr">
-        <is>
-          <t>hospital</t>
-        </is>
-      </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>Polygon</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>13.6978931</t>
+          <t>13.7874613</t>
         </is>
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>-88.10190785</t>
+          <t>-88.1379986</t>
         </is>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>centroide_area</t>
+          <t>coordenada_original</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>POLYGON ((-88.1015783 13.6984618, -88.1022721 13.6984445, -88.1022433 13.6973338, -88.101528 13.6973426, -88.1015382 13.6975709, -88.1015533 13.6975703, -88.1015783 13.6984618))</t>
+          <t>POINT (-88.1379986 13.7874613)</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/relation/8328359</t>
+          <t>https://www.openstreetmap.org/node/3972391822</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=13.6978931,-88.10190785</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=13.7874613,-88.1379986</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>hot-way-850616743</t>
+          <t>hot-node-4317174888</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2844,32 +2844,32 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>way/850616743</t>
+          <t>node/4317174888</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>sibasi</t>
+          <t>CAIPES Clinic</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Clínica</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>otro</t>
+          <t>clinica</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Polígono</t>
+          <t>Punto</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>poligono</t>
+          <t>punto</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -2879,7 +2879,7 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>San Francisco Gotera</t>
+          <t>Cacaopera</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -2889,49 +2889,49 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>Polygon</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>13.69862207</t>
+          <t>13.795529</t>
         </is>
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>-88.10189578</t>
+          <t>-88.0424141</t>
         </is>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>centroide_area</t>
+          <t>coordenada_original</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>POLYGON ((-88.1021602 13.6987283, -88.102248 13.6984719, -88.1016197 13.6984768, -88.1016163 13.6988229, -88.1021602 13.6987283))</t>
+          <t>POINT (-88.0424141 13.795529)</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/way/850616743</t>
+          <t>https://www.openstreetmap.org/node/4317174888</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=13.69862207,-88.10189578</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=13.795529,-88.0424141</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>hot-node-3972391822</t>
+          <t>hot-node-8819299377</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2941,12 +2941,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>node/3972391822</t>
+          <t>node/8819299377</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Unidad de Salud</t>
+          <t>UCSF CARRIZAL</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -2976,7 +2976,7 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Delicias de Concepción</t>
+          <t>San Simón</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -2984,6 +2984,16 @@
           <t>Oriental</t>
         </is>
       </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>Público</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Medicina general</t>
+        </is>
+      </c>
       <c r="T26" t="inlineStr">
         <is>
           <t>Point</t>
@@ -2996,12 +3006,12 @@
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>13.7874613</t>
+          <t>13.798957</t>
         </is>
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>-88.1379986</t>
+          <t>-88.244094</t>
         </is>
       </c>
       <c r="X26" t="inlineStr">
@@ -3011,24 +3021,24 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>POINT (-88.1379986 13.7874613)</t>
+          <t>POINT (-88.244094 13.798957)</t>
         </is>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/node/3972391822</t>
+          <t>https://www.openstreetmap.org/node/8819299377</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=13.7874613,-88.1379986</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=13.798957,-88.244094</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>hot-node-4317174888</t>
+          <t>hot-node-8819299349</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3038,12 +3048,12 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>node/4317174888</t>
+          <t>node/8819299349</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>CAIPES Clinic</t>
+          <t>UCSF QUEBRADAS</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -3073,7 +3083,7 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Cacaopera</t>
+          <t>San Simón</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -3081,6 +3091,16 @@
           <t>Oriental</t>
         </is>
       </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>Público</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Medicina general</t>
+        </is>
+      </c>
       <c r="T27" t="inlineStr">
         <is>
           <t>Point</t>
@@ -3093,12 +3113,12 @@
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>13.795529</t>
+          <t>13.8029393</t>
         </is>
       </c>
       <c r="W27" t="inlineStr">
         <is>
-          <t>-88.0424141</t>
+          <t>-88.2334101</t>
         </is>
       </c>
       <c r="X27" t="inlineStr">
@@ -3108,24 +3128,24 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>POINT (-88.0424141 13.795529)</t>
+          <t>POINT (-88.2334101 13.8029393)</t>
         </is>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/node/4317174888</t>
+          <t>https://www.openstreetmap.org/node/8819299349</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=13.795529,-88.0424141</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=13.8029393,-88.2334101</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>hot-node-8819299377</t>
+          <t>hot-node-3972011219</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3135,12 +3155,12 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>node/8819299377</t>
+          <t>node/3972011219</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>UCSF CARRIZAL</t>
+          <t>UCSF</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -3170,7 +3190,7 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>San Simón</t>
+          <t>Gualococti</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -3183,11 +3203,6 @@
           <t>Público</t>
         </is>
       </c>
-      <c r="P28" t="inlineStr">
-        <is>
-          <t>Medicina general</t>
-        </is>
-      </c>
       <c r="T28" t="inlineStr">
         <is>
           <t>Point</t>
@@ -3200,12 +3215,12 @@
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>13.798957</t>
+          <t>13.8178009</t>
         </is>
       </c>
       <c r="W28" t="inlineStr">
         <is>
-          <t>-88.244094</t>
+          <t>-88.2104818</t>
         </is>
       </c>
       <c r="X28" t="inlineStr">
@@ -3215,24 +3230,24 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>POINT (-88.244094 13.798957)</t>
+          <t>POINT (-88.2104818 13.8178009)</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/node/8819299377</t>
+          <t>https://www.openstreetmap.org/node/3972011219</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=13.798957,-88.244094</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=13.8178009,-88.2104818</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>hot-node-8819299349</t>
+          <t>hot-node-3971434373</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3242,12 +3257,12 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>node/8819299349</t>
+          <t>node/3971434373</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>UCSF QUEBRADAS</t>
+          <t>Unidad de Salud</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -3285,16 +3300,6 @@
           <t>Oriental</t>
         </is>
       </c>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>Público</t>
-        </is>
-      </c>
-      <c r="P29" t="inlineStr">
-        <is>
-          <t>Medicina general</t>
-        </is>
-      </c>
       <c r="T29" t="inlineStr">
         <is>
           <t>Point</t>
@@ -3307,12 +3312,12 @@
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>13.8029393</t>
+          <t>13.8324505</t>
         </is>
       </c>
       <c r="W29" t="inlineStr">
         <is>
-          <t>-88.2334101</t>
+          <t>-88.227521</t>
         </is>
       </c>
       <c r="X29" t="inlineStr">
@@ -3322,24 +3327,24 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>POINT (-88.2334101 13.8029393)</t>
+          <t>POINT (-88.227521 13.8324505)</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/node/8819299349</t>
+          <t>https://www.openstreetmap.org/node/3971434373</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=13.8029393,-88.2334101</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=13.8324505,-88.227521</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>hot-node-3972011219</t>
+          <t>hot-node-3971971763</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3349,12 +3354,12 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>node/3972011219</t>
+          <t>node/3971971763</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>UCSF</t>
+          <t>Unidad de Salud</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -3384,7 +3389,7 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>Gualococti</t>
+          <t>Meanguera</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -3392,11 +3397,6 @@
           <t>Oriental</t>
         </is>
       </c>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>Público</t>
-        </is>
-      </c>
       <c r="T30" t="inlineStr">
         <is>
           <t>Point</t>
@@ -3409,12 +3409,12 @@
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>13.8178009</t>
+          <t>13.8512283</t>
         </is>
       </c>
       <c r="W30" t="inlineStr">
         <is>
-          <t>-88.2104818</t>
+          <t>-88.1533126</t>
         </is>
       </c>
       <c r="X30" t="inlineStr">
@@ -3424,24 +3424,24 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>POINT (-88.2104818 13.8178009)</t>
+          <t>POINT (-88.1533126 13.8512283)</t>
         </is>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/node/3972011219</t>
+          <t>https://www.openstreetmap.org/node/3971971763</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=13.8178009,-88.2104818</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=13.8512283,-88.1533126</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>hot-node-3971434373</t>
+          <t>hot-node-3972158089</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3451,7 +3451,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>node/3971434373</t>
+          <t>node/3972158089</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -3486,7 +3486,7 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>San Simón</t>
+          <t>Joateca</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -3506,12 +3506,12 @@
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>13.8324505</t>
+          <t>13.8952454</t>
         </is>
       </c>
       <c r="W31" t="inlineStr">
         <is>
-          <t>-88.227521</t>
+          <t>-88.0463754</t>
         </is>
       </c>
       <c r="X31" t="inlineStr">
@@ -3521,24 +3521,24 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>POINT (-88.227521 13.8324505)</t>
+          <t>POINT (-88.0463754 13.8952454)</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/node/3971434373</t>
+          <t>https://www.openstreetmap.org/node/3972158089</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=13.8324505,-88.227521</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=13.8952454,-88.0463754</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>hot-node-3971971763</t>
+          <t>hot-node-7223662570</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>node/3971971763</t>
+          <t>node/7223662570</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Unidad de Salud</t>
+          <t>Clinica El Mozote</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -3591,6 +3591,16 @@
           <t>Oriental</t>
         </is>
       </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>Público</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Medicina general</t>
+        </is>
+      </c>
       <c r="T32" t="inlineStr">
         <is>
           <t>Point</t>
@@ -3603,12 +3613,12 @@
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>13.8512283</t>
+          <t>13.8988504</t>
         </is>
       </c>
       <c r="W32" t="inlineStr">
         <is>
-          <t>-88.1533126</t>
+          <t>-88.1144685</t>
         </is>
       </c>
       <c r="X32" t="inlineStr">
@@ -3618,24 +3628,24 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>POINT (-88.1533126 13.8512283)</t>
+          <t>POINT (-88.1144685 13.8988504)</t>
         </is>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/node/3971971763</t>
+          <t>https://www.openstreetmap.org/node/7223662570</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=13.8512283,-88.1533126</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=13.8988504,-88.1144685</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>hot-node-3972158089</t>
+          <t>hot-node-3971704870</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3645,7 +3655,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>node/3972158089</t>
+          <t>node/3971704870</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -3680,7 +3690,7 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Joateca</t>
+          <t>Torola</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -3700,12 +3710,12 @@
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>13.8952454</t>
+          <t>13.9134905</t>
         </is>
       </c>
       <c r="W33" t="inlineStr">
         <is>
-          <t>-88.0463754</t>
+          <t>-88.233072</t>
         </is>
       </c>
       <c r="X33" t="inlineStr">
@@ -3715,24 +3725,24 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>POINT (-88.0463754 13.8952454)</t>
+          <t>POINT (-88.233072 13.9134905)</t>
         </is>
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/node/3972158089</t>
+          <t>https://www.openstreetmap.org/node/3971704870</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=13.8952454,-88.0463754</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=13.9134905,-88.233072</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>hot-node-7223662570</t>
+          <t>hot-node-3972290289</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3742,12 +3752,12 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>node/7223662570</t>
+          <t>node/3972290289</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Clinica El Mozote</t>
+          <t>Unidad de Salud</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -3777,7 +3787,7 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Meanguera</t>
+          <t>Arambala</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -3790,11 +3800,6 @@
           <t>Público</t>
         </is>
       </c>
-      <c r="P34" t="inlineStr">
-        <is>
-          <t>Medicina general</t>
-        </is>
-      </c>
       <c r="T34" t="inlineStr">
         <is>
           <t>Point</t>
@@ -3807,12 +3812,12 @@
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>13.8988504</t>
+          <t>13.9218386</t>
         </is>
       </c>
       <c r="W34" t="inlineStr">
         <is>
-          <t>-88.1144685</t>
+          <t>-88.1322185</t>
         </is>
       </c>
       <c r="X34" t="inlineStr">
@@ -3822,24 +3827,24 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>POINT (-88.1144685 13.8988504)</t>
+          <t>POINT (-88.1322185 13.9218386)</t>
         </is>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/node/7223662570</t>
+          <t>https://www.openstreetmap.org/node/3972290289</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=13.8988504,-88.1144685</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=13.9218386,-88.1322185</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>hot-node-3971704870</t>
+          <t>hot-node-4028228735</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3849,7 +3854,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>node/3971704870</t>
+          <t>node/4028228735</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -3884,7 +3889,7 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Torola</t>
+          <t>Perquín</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -3904,12 +3909,12 @@
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>13.9134905</t>
+          <t>13.9613285</t>
         </is>
       </c>
       <c r="W35" t="inlineStr">
         <is>
-          <t>-88.233072</t>
+          <t>-88.1957679</t>
         </is>
       </c>
       <c r="X35" t="inlineStr">
@@ -3919,24 +3924,24 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>POINT (-88.233072 13.9134905)</t>
+          <t>POINT (-88.1957679 13.9613285)</t>
         </is>
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/node/3971704870</t>
+          <t>https://www.openstreetmap.org/node/4028228735</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=13.9134905,-88.233072</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=13.9613285,-88.1957679</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>hot-node-3972290289</t>
+          <t>hot-node-4026961607</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3946,7 +3951,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>node/3972290289</t>
+          <t>node/4026961607</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -3981,7 +3986,7 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Arambala</t>
+          <t>Sensembra</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -3989,11 +3994,6 @@
           <t>Oriental</t>
         </is>
       </c>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>Público</t>
-        </is>
-      </c>
       <c r="T36" t="inlineStr">
         <is>
           <t>Point</t>
@@ -4006,12 +4006,12 @@
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>13.9218386</t>
+          <t>13.665148</t>
         </is>
       </c>
       <c r="W36" t="inlineStr">
         <is>
-          <t>-88.1322185</t>
+          <t>-88.1698087</t>
         </is>
       </c>
       <c r="X36" t="inlineStr">
@@ -4021,24 +4021,24 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>POINT (-88.1322185 13.9218386)</t>
+          <t>POINT (-88.1698087 13.665148)</t>
         </is>
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/node/3972290289</t>
+          <t>https://www.openstreetmap.org/node/4026961607</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=13.9218386,-88.1322185</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=13.665148,-88.1698087</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>hot-node-4028228735</t>
+          <t>hot-node-3971795338</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4048,12 +4048,12 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>node/4028228735</t>
+          <t>node/3971795338</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Unidad de Salud</t>
+          <t>Cruz Roja Salvadoreña</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -4083,7 +4083,7 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Perquín</t>
+          <t>San Francisco Gotera</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -4103,12 +4103,12 @@
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>13.9613285</t>
+          <t>13.6880416</t>
         </is>
       </c>
       <c r="W37" t="inlineStr">
         <is>
-          <t>-88.1957679</t>
+          <t>-88.0977761</t>
         </is>
       </c>
       <c r="X37" t="inlineStr">
@@ -4118,24 +4118,24 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>POINT (-88.1957679 13.9613285)</t>
+          <t>POINT (-88.0977761 13.6880416)</t>
         </is>
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/node/4028228735</t>
+          <t>https://www.openstreetmap.org/node/3971795338</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=13.9613285,-88.1957679</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=13.6880416,-88.0977761</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>hot-node-4026961607</t>
+          <t>hot-node-3971789068</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4145,22 +4145,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>node/4026961607</t>
+          <t>node/3971789068</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Unidad de Salud</t>
+          <t>Sin nombre</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Clínica</t>
+          <t>Hospital</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>clinica</t>
+          <t>hospital</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -4180,7 +4180,7 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>Sensembra</t>
+          <t>San Francisco Gotera</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="V38" t="inlineStr">
         <is>
-          <t>13.665148</t>
+          <t>13.6950674</t>
         </is>
       </c>
       <c r="W38" t="inlineStr">
         <is>
-          <t>-88.1698087</t>
+          <t>-88.102132</t>
         </is>
       </c>
       <c r="X38" t="inlineStr">
@@ -4215,24 +4215,24 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>POINT (-88.1698087 13.665148)</t>
+          <t>POINT (-88.102132 13.6950674)</t>
         </is>
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/node/4026961607</t>
+          <t>https://www.openstreetmap.org/node/3971789068</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=13.665148,-88.1698087</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=13.6950674,-88.102132</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>hot-node-3971795338</t>
+          <t>hot-node-3971759964</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4242,12 +4242,12 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>node/3971795338</t>
+          <t>node/3971759964</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Cruz Roja Salvadoreña</t>
+          <t>Sin nombre</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -4297,12 +4297,12 @@
       </c>
       <c r="V39" t="inlineStr">
         <is>
-          <t>13.6880416</t>
+          <t>13.6959013</t>
         </is>
       </c>
       <c r="W39" t="inlineStr">
         <is>
-          <t>-88.0977761</t>
+          <t>-88.1021642</t>
         </is>
       </c>
       <c r="X39" t="inlineStr">
@@ -4312,24 +4312,24 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>POINT (-88.0977761 13.6880416)</t>
+          <t>POINT (-88.1021642 13.6959013)</t>
         </is>
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/node/3971795338</t>
+          <t>https://www.openstreetmap.org/node/3971759964</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=13.6880416,-88.0977761</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=13.6959013,-88.1021642</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>hot-node-3971789068</t>
+          <t>hot-node-9115322867</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4339,22 +4339,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>node/3971789068</t>
+          <t>node/9115322867</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Sin nombre</t>
+          <t>CENTRO VACUNACION COVID-19</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Hospital</t>
+          <t>Clínica</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>hospital</t>
+          <t>clinica</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -4382,6 +4382,11 @@
           <t>Oriental</t>
         </is>
       </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>Público</t>
+        </is>
+      </c>
       <c r="T40" t="inlineStr">
         <is>
           <t>Point</t>
@@ -4394,12 +4399,12 @@
       </c>
       <c r="V40" t="inlineStr">
         <is>
-          <t>13.6950674</t>
+          <t>13.6974925</t>
         </is>
       </c>
       <c r="W40" t="inlineStr">
         <is>
-          <t>-88.102132</t>
+          <t>-88.1014697</t>
         </is>
       </c>
       <c r="X40" t="inlineStr">
@@ -4409,24 +4414,24 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>POINT (-88.102132 13.6950674)</t>
+          <t>POINT (-88.1014697 13.6974925)</t>
         </is>
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/node/3971789068</t>
+          <t>https://www.openstreetmap.org/node/9115322867</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=13.6950674,-88.102132</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=13.6974925,-88.1014697</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>hot-node-3971759964</t>
+          <t>hot-node-9115322866</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4436,12 +4441,12 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>node/3971759964</t>
+          <t>node/9115322866</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Sin nombre</t>
+          <t>UCSF GOTERA/CENTRO DE VACUNACION COVID</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -4479,6 +4484,11 @@
           <t>Oriental</t>
         </is>
       </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>Público</t>
+        </is>
+      </c>
       <c r="T41" t="inlineStr">
         <is>
           <t>Point</t>
@@ -4491,12 +4501,12 @@
       </c>
       <c r="V41" t="inlineStr">
         <is>
-          <t>13.6959013</t>
+          <t>13.6977383</t>
         </is>
       </c>
       <c r="W41" t="inlineStr">
         <is>
-          <t>-88.1021642</t>
+          <t>-88.1054594</t>
         </is>
       </c>
       <c r="X41" t="inlineStr">
@@ -4506,24 +4516,24 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>POINT (-88.1021642 13.6959013)</t>
+          <t>POINT (-88.1054594 13.6977383)</t>
         </is>
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/node/3971759964</t>
+          <t>https://www.openstreetmap.org/node/9115322866</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=13.6959013,-88.1021642</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=13.6977383,-88.1054594</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>hot-node-9115322867</t>
+          <t>hot-node-3971364159</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4533,12 +4543,12 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>node/9115322867</t>
+          <t>node/3971364159</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>CENTRO VACUNACION COVID-19</t>
+          <t>Unidad de Salud</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -4568,7 +4578,7 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>San Francisco Gotera</t>
+          <t>Sociedad</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -4576,11 +4586,6 @@
           <t>Oriental</t>
         </is>
       </c>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>Público</t>
-        </is>
-      </c>
       <c r="T42" t="inlineStr">
         <is>
           <t>Point</t>
@@ -4593,12 +4598,12 @@
       </c>
       <c r="V42" t="inlineStr">
         <is>
-          <t>13.6974925</t>
+          <t>13.7024886</t>
         </is>
       </c>
       <c r="W42" t="inlineStr">
         <is>
-          <t>-88.1014697</t>
+          <t>-88.0062527</t>
         </is>
       </c>
       <c r="X42" t="inlineStr">
@@ -4608,24 +4613,24 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>POINT (-88.1014697 13.6974925)</t>
+          <t>POINT (-88.0062527 13.7024886)</t>
         </is>
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/node/9115322867</t>
+          <t>https://www.openstreetmap.org/node/3971364159</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=13.6974925,-88.1014697</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=13.7024886,-88.0062527</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>hot-node-9115322866</t>
+          <t>hot-node-3971683759</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4635,12 +4640,12 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>node/9115322866</t>
+          <t>node/3971683759</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>UCSF GOTERA/CENTRO DE VACUNACION COVID</t>
+          <t>Unidad de Salud</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -4670,7 +4675,7 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>San Francisco Gotera</t>
+          <t>Chilanga</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -4678,11 +4683,6 @@
           <t>Oriental</t>
         </is>
       </c>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>Público</t>
-        </is>
-      </c>
       <c r="T43" t="inlineStr">
         <is>
           <t>Point</t>
@@ -4695,12 +4695,12 @@
       </c>
       <c r="V43" t="inlineStr">
         <is>
-          <t>13.6977383</t>
+          <t>13.7214664</t>
         </is>
       </c>
       <c r="W43" t="inlineStr">
         <is>
-          <t>-88.1054594</t>
+          <t>-88.120843</t>
         </is>
       </c>
       <c r="X43" t="inlineStr">
@@ -4710,24 +4710,24 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>POINT (-88.1054594 13.6977383)</t>
+          <t>POINT (-88.120843 13.7214664)</t>
         </is>
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/node/9115322866</t>
+          <t>https://www.openstreetmap.org/node/3971683759</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=13.6977383,-88.1054594</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=13.7214664,-88.120843</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>hot-node-3971364159</t>
+          <t>hot-node-7935411967</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4737,12 +4737,12 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>node/3971364159</t>
+          <t>node/7935411967</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Unidad de Salud</t>
+          <t>Sin nombre</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -4772,7 +4772,7 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>Sociedad</t>
+          <t>Lolotiquillo</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -4792,12 +4792,12 @@
       </c>
       <c r="V44" t="inlineStr">
         <is>
-          <t>13.7024886</t>
+          <t>13.7245699</t>
         </is>
       </c>
       <c r="W44" t="inlineStr">
         <is>
-          <t>-88.0062527</t>
+          <t>-88.0905386</t>
         </is>
       </c>
       <c r="X44" t="inlineStr">
@@ -4807,24 +4807,24 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>POINT (-88.0062527 13.7024886)</t>
+          <t>POINT (-88.0905386 13.7245699)</t>
         </is>
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/node/3971364159</t>
+          <t>https://www.openstreetmap.org/node/7935411967</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=13.7024886,-88.0062527</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=13.7245699,-88.0905386</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>hot-node-3971683759</t>
+          <t>hot-node-4035719727</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4834,7 +4834,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>node/3971683759</t>
+          <t>node/4035719727</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -4869,7 +4869,7 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>Chilanga</t>
+          <t>Yoloaiquín</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="V45" t="inlineStr">
         <is>
-          <t>13.7214664</t>
+          <t>13.7675416</t>
         </is>
       </c>
       <c r="W45" t="inlineStr">
         <is>
-          <t>-88.120843</t>
+          <t>-88.126272</t>
         </is>
       </c>
       <c r="X45" t="inlineStr">
@@ -4904,24 +4904,24 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>POINT (-88.120843 13.7214664)</t>
+          <t>POINT (-88.126272 13.7675416)</t>
         </is>
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/node/3971683759</t>
+          <t>https://www.openstreetmap.org/node/4035719727</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=13.7214664,-88.120843</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=13.7675416,-88.126272</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>hot-node-7935411967</t>
+          <t>hot-node-11346718336</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4931,7 +4931,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>node/7935411967</t>
+          <t>node/11346718336</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -4941,12 +4941,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Clínica</t>
+          <t>Otro</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>clinica</t>
+          <t>otro</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -4966,7 +4966,7 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>Lolotiquillo</t>
+          <t>Cacaopera</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -4986,12 +4986,12 @@
       </c>
       <c r="V46" t="inlineStr">
         <is>
-          <t>13.7245699</t>
+          <t>13.7680061</t>
         </is>
       </c>
       <c r="W46" t="inlineStr">
         <is>
-          <t>-88.0905386</t>
+          <t>-88.0664796</t>
         </is>
       </c>
       <c r="X46" t="inlineStr">
@@ -5001,24 +5001,24 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>POINT (-88.0905386 13.7245699)</t>
+          <t>POINT (-88.0664796 13.7680061)</t>
         </is>
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/node/7935411967</t>
+          <t>https://www.openstreetmap.org/node/11346718336</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=13.7245699,-88.0905386</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=13.7680061,-88.0664796</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>hot-node-4035719727</t>
+          <t>hot-node-6916841199</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -5028,12 +5028,12 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>node/4035719727</t>
+          <t>node/6916841199</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Unidad de Salud</t>
+          <t>UCSF Cacaopera</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -5063,7 +5063,7 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>Yoloaiquín</t>
+          <t>Cacaopera</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -5071,6 +5071,11 @@
           <t>Oriental</t>
         </is>
       </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>Cacaopera</t>
+        </is>
+      </c>
       <c r="T47" t="inlineStr">
         <is>
           <t>Point</t>
@@ -5083,12 +5088,12 @@
       </c>
       <c r="V47" t="inlineStr">
         <is>
-          <t>13.7675416</t>
+          <t>13.7749276</t>
         </is>
       </c>
       <c r="W47" t="inlineStr">
         <is>
-          <t>-88.126272</t>
+          <t>-88.0823146</t>
         </is>
       </c>
       <c r="X47" t="inlineStr">
@@ -5098,221 +5103,22 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>POINT (-88.126272 13.7675416)</t>
+          <t>POINT (-88.0823146 13.7749276)</t>
         </is>
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/node/4035719727</t>
+          <t>https://www.openstreetmap.org/node/6916841199</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
-        <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=13.7675416,-88.126272</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>hot-node-11346718336</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>hot</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>node/11346718336</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>Sin nombre</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>Otro</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>otro</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>Punto</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>punto</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>Morazán</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>Cacaopera</t>
-        </is>
-      </c>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>Oriental</t>
-        </is>
-      </c>
-      <c r="T48" t="inlineStr">
-        <is>
-          <t>Point</t>
-        </is>
-      </c>
-      <c r="U48" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="V48" t="inlineStr">
-        <is>
-          <t>13.7680061</t>
-        </is>
-      </c>
-      <c r="W48" t="inlineStr">
-        <is>
-          <t>-88.0664796</t>
-        </is>
-      </c>
-      <c r="X48" t="inlineStr">
-        <is>
-          <t>coordenada_original</t>
-        </is>
-      </c>
-      <c r="Y48" t="inlineStr">
-        <is>
-          <t>POINT (-88.0664796 13.7680061)</t>
-        </is>
-      </c>
-      <c r="Z48" t="inlineStr">
-        <is>
-          <t>https://www.openstreetmap.org/node/11346718336</t>
-        </is>
-      </c>
-      <c r="AA48" t="inlineStr">
-        <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=13.7680061,-88.0664796</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>hot-node-6916841199</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>hot</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>node/6916841199</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>UCSF Cacaopera</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>Clínica</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>clinica</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>Punto</t>
-        </is>
-      </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>punto</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>Morazán</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>Cacaopera</t>
-        </is>
-      </c>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>Oriental</t>
-        </is>
-      </c>
-      <c r="L49" t="inlineStr">
-        <is>
-          <t>Cacaopera</t>
-        </is>
-      </c>
-      <c r="T49" t="inlineStr">
-        <is>
-          <t>Point</t>
-        </is>
-      </c>
-      <c r="U49" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="V49" t="inlineStr">
-        <is>
-          <t>13.7749276</t>
-        </is>
-      </c>
-      <c r="W49" t="inlineStr">
-        <is>
-          <t>-88.0823146</t>
-        </is>
-      </c>
-      <c r="X49" t="inlineStr">
-        <is>
-          <t>coordenada_original</t>
-        </is>
-      </c>
-      <c r="Y49" t="inlineStr">
-        <is>
-          <t>POINT (-88.0823146 13.7749276)</t>
-        </is>
-      </c>
-      <c r="Z49" t="inlineStr">
-        <is>
-          <t>https://www.openstreetmap.org/node/6916841199</t>
-        </is>
-      </c>
-      <c r="AA49" t="inlineStr">
         <is>
           <t>https://www.google.com/maps/search/?api=1&amp;query=13.7749276,-88.0823146</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AA49"/>
+  <autoFilter ref="A1:AA47"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>